--- a/setup/categorisation/Fergal-Pharmacist-Calls.xlsx
+++ b/setup/categorisation/Fergal-Pharmacist-Calls.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Veterinary products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Is this a medicine" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Veterinary products'!$A$3:$H$10</definedName>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +43,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +64,12 @@
         <fgColor rgb="00FFF2A8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2A8"/>
+        <bgColor rgb="00FFF2A8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -73,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -89,6 +99,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,4 +781,1183 @@
   <autoFilter ref="A3:H10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>46 products held out of the welcome discount, pending a pharmacist call</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>These 46 products are in Medicines &amp; Health but are not tagged pharmacist-review, so the store does not treat them as medicines: no questions before purchase, and they would be discountable. We could not confirm they are not medicines, so they are held out of the WELCOME10 welcome discount by a second tag, no-welcome-discount. That tag is a holding position, not an answer. The question is column F. If any of these should be pharmacist-review, it needs the questions before purchase as well, which matters more than the discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>The tagging disagrees with itself inside brands, which is why this tab exists: Nelsons Arnicare 50G Cream is tagged and Arnicare Arnica Cream 30G is not; Uniflu With Vitamin C Tablets 24Pk is tagged and Uniflu Cough Stop is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Type now</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>pharmacist-review now?</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Why we held it</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Should this be pharmacist-review?</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Your notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Arnicare Arnica Cream 30G</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Pain Relief</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>named by the client (tagging contradicts itself within the brand)</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Bloateze Tablets 20Pk Phoenix</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Stomach &amp; Digestion</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>ingested active</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Burnshield Hydrogel 50Ml</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Medicated Skincare</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>treats a named condition; medicinal status unclear</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Celtic Wind Cbd Oil 5% 10Ml</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Pain Relief</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>ingested active</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Cerumol Ear Drops</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Eye &amp; Ear Care</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the ear</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Cerumol Olive Oil Ear Drops 10Ml</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Eye &amp; Ear Care</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the ear</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Cl-Ear Ear Relief Drops</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Eye &amp; Ear Care</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the ear</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Cl-Ear Express Dual Action Ear Drops</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Eye &amp; Ear Care</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the ear</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Cl-Ear Olive Oil Ear Drops</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Eye &amp; Ear Care</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the ear</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Cydonia Soothing Arnica Ultra Gel 100Ml</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Pain Relief</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>treats a named condition; medicinal status unclear</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Full Marks Solution 100Ml</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Sensitive Conditions</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>head-lice insecticide</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Full Marks Solution 200Ml</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Sensitive Conditions</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>head-lice insecticide</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Fusion Allergy Eye Drops</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Allergy Relief</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the eye</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Fusion Allergy Eye Spray 10Ml</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Allergy Relief</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the eye</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Fusion Allergy Lozenges 24</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Allergy Relief</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>nasal or oral spray with an active</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Fusion Allergy Nasal Spray 20Ml</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Allergy Relief</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>nasal or oral spray with an active</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Gelorevoice Blackcurrant</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Cold &amp; Flu</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>nasal or oral spray with an active</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Gelorevoice Cherry</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Cold &amp; Flu</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>nasal or oral spray with an active</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Hylo Care 0.1%/2% Eye Drops 7.5Ml</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Eye &amp; Ear Care</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the eye</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Hylo Dual Pres Free Eye Drops 7.5Ml 0.05%</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Eye &amp; Ear Care</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the eye</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Hylo Night Ointment</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Eye &amp; Ear Care</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the eye</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Hylo Tear 0.1% Eye Drops 7.5Ml</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Eye &amp; Ear Care</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the eye</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Hylo-Forte Lubricating Eye Drops 7.5Ml</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Eye &amp; Ear Care</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the eye</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Kidsner Anti Allergic Spray</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Children's Medicine</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>filed under Children's Medicine</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Kidsner Cooling Foam For Chickenpox 100Ml</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Children's Medicine</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>filed under Children's Medicine</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Nelsons Arnicare 50G Cream</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; First Aid</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>named by the client (tagging contradicts itself within the brand)</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Nelsons Arnicare Cooling Gel 30G</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; First Aid</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>named by the client (tagging contradicts itself within the brand)</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Nubit</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Pain Relief</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>unidentified product, name suggests a medicine</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Optase Allergy Eye Drop 0.5Mlsdu</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Eye &amp; Ear Care</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the eye</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Papilocare Vaginal Gel</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>treats a named condition; medicinal status unclear</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Preparation H Gel 25G</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Stomach &amp; Digestion</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>named by the client (tagging contradicts itself within the brand)</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Preparation H Gel 50G</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Sensitive Conditions</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>named by the client (tagging contradicts itself within the brand)</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Preparation H Ointment 25G</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Sensitive Conditions</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>named by the client (tagging contradicts itself within the brand)</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Sorefix Rescue Cold Sore Cream</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Cold &amp; Flu</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>treats a named condition; medicinal status unclear</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Sreeze Nasal Spray 10Ml</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Allergy Relief</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>nasal or oral spray with an active</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Sreeze Oral Strips 14Pk</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Sensitive Conditions</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>nasal or oral spray with an active</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Tears Naturale 15Ml Eye Drops</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Eye &amp; Ear Care</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the eye</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Thealoz Duo Gel 0.4G 30Pk</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Eye &amp; Ear Care</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>instilled into the eye</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Tramma Gel</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Pain Relief</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>unidentified product, name suggests a medicine</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Ultrapure Hydrogen Peroxide130ml</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Medicated Skincare</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>treats a named condition; medicinal status unclear</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Uniflu Cough Stop</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Cold &amp; Flu</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>named by the client (tagging contradicts itself within the brand)</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Uniflu Immune Defence</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Supplements &gt; Immune Support</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>named by the client (tagging contradicts itself within the brand)</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Uniflu With Vitamin C Tablets 24Pk</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Cold &amp; Flu</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>named by the client (tagging contradicts itself within the brand)</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Vamousse Head Lice Treatment Mousse</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Children's Medicine</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>filed under Children's Medicine</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Virasoothe Gel</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy &gt; Children's Medicine</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>filed under Children's Medicine</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Wartner Wart &amp; Verruca Cryo Freeze Pen</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>treats a named condition; medicinal status unclear</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>